--- a/extenbooks/S603_extenbook.xlsx
+++ b/extenbooks/S603_extenbook.xlsx
@@ -7860,7 +7860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A97"/>
+  <dimension ref="A1:A96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7899,480 +7899,477 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Status:** ingested  **Year range (book):** 1947-2011</t>
+          <t>***Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Component Ratios x1, x2, x3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Component Ratios x1, x2, x3</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>## Why It Matters</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>## Why It Matters</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fig 6.3 source. x1 freezes when NMINT_corp from T7.11 incomplete (do NOT forward-fill). Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fig 6.3 source. x1 freezes when NMINT_corp from T7.11 incomplete (do NOT forward-fill). Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>## Sources (per subseries)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>## Sources (per subseries)</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+          <t>|-----------|---------------|----------|---------------|-------|</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>|-----------|---------------|----------|---------------|-------|</t>
+          <t>| S603-A | II7 | `x1` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| S603-A | II7 | `x1` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S603-B | II7 | `x2` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| S603-B | II7 | `x2` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S603-C | II7 | `x3` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| S603-C | II7 | `x3` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S603-D | II7 | `x3*(x1 / x2)` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>| S603-D | II7 | `x3*(x1 / x2)` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Decomposition of rcorp/rcorpnipa = (x1/x2) * x3 per eq. 6.11. x1 = 1 + NMINT/P (imputed-interest factor); x2 = 1 + INV(-1)/KNCbea(-1) (inventory factor); x3 = KNCbea(-1)/KGC(-1) (BEA vs GPIM revaluation). x1 freezes at last complete NMINT year (CD2 known issue, preserved).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Decomposition of rcorp/rcorpnipa = (x1/x2) * x3 per eq. 6.11. x1 = 1 + NMINT/P (imputed-interest factor); x2 = 1 + INV(-1)/KNCbea(-1) (inventory factor); x3 = KNCbea(-1)/KGC(-1) (BEA vs GPIM revaluation). x1 freezes at last complete NMINT year (CD2 known issue, preserved).</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>## Year Coverage</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>## Year Coverage</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Book period: 1947-2011. Vintage-stable extension recipe in `S603_EPR.md`.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Book period: 1947-2011. Vintage-stable extension recipe in `S603_EPR.md`.</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>## Units</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>## Units</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dimensionless_ratio</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dimensionless_ratio</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>## Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>## Caveats</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>* x1 freezes at last complete NMINT_corp year; do NOT forward-fill (CD2 preserved behaviour).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>* x1 freezes at last complete NMINT_corp year; do NOT forward-fill (CD2 preserved behaviour).</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>`AS003`, `AS004`, `AS009`</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>`AS003`, `AS004`, `AS009`</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>## Validation Expectation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>## Validation Expectation</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>`V03_S603_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4">
+    <row r="52">
+      <c r="A52" s="4">
         <f>== EPR: S603_EPR.md ===</f>
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t># S603 — Component Ratios x1, x2, x3 (Extension Provenance Record)</t>
+        </is>
+      </c>
+    </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t># S603 — Component Ratios x1, x2, x3 (Extension Provenance Record)</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>## Method</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S603 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S603 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>3. Re-run the construction formula end-to-end.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
+          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
+          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
+          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>## Worked Example</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>## Worked Example</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>For S603, the Phase 5 round-trip validation reads `S603_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>For S603, the Phase 5 round-trip validation reads `S603_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>## No-Proxy Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>## No-Proxy Disclosure</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>## No-Synthetic Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>## No-Synthetic Disclosure</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>## Failure Mode Table</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>## Failure Mode Table</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Response |</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Response |</t>
+          <t>|---------|-----------|----------|</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>|---------|-----------|----------|</t>
+          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>## CD2 Divergence Pre-Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>## Anti-Degradation Compliance</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>## Anti-Degradation Compliance</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
         </is>
@@ -8795,11 +8792,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8822,76 +8819,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Component Ratios x1, x2, x3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S603_research.json", "adequacy_report": "Technical/docs/chapters/CH6_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S603_DPR.md", "epr": "Technical/docs/series/S603_EPR.md", "loader": "Technical/code/L01_loaders/L01_S603_load.py", "processor": "Technical/code/P02_processors/P02_S603_construct.py", "validator": "Technical/code/V03_validators/V03_S603_validate.py", "processed": "Technical/data/processed/S603.parquet", "chopped_csv": "Technical/chopped/S603.csv", "extenbook_xlsx": "Technical/extenbooks/S603_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:43:17.420354+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S603_extenbook.xlsx
+++ b/extenbooks/S603_extenbook.xlsx
@@ -7860,7 +7860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A96"/>
+  <dimension ref="A1:A120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7936,7 +7936,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fig 6.3 source. x1 freezes when NMINT_corp from T7.11 incomplete (do NOT forward-fill). Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Source figure: Fig 6.3. The ratio x1 is frozen (held, not forward-filled) in any year where corporate net monetary interest (NMINT) from National Income and Product Accounts table 7.11 is incomplete. The book-period values are transcribed verbatim from Shaikh's published Appendix 6.8 (sub-table II.7). See `CH6_GPIM_SUMMARY.md` for the full Chapter 6 construction pipeline.</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Decomposition of rcorp/rcorpnipa = (x1/x2) * x3 per eq. 6.11. x1 = 1 + NMINT/P (imputed-interest factor); x2 = 1 + INV(-1)/KNCbea(-1) (inventory factor); x3 = KNCbea(-1)/KGC(-1) (BEA vs GPIM revaluation). x1 freezes at last complete NMINT year (CD2 known issue, preserved).</t>
+          <t>Decomposition of the corporate profit-rate ratio rcorp/rcorpnipa = (x1/x2) × x3 per Shaikh's eq. 6.11, where x1 = 1 + NMINT/P (net-monetary-interest factor); x2 = 1 + INV[t-1]/KNCbea[t-1] (inventory factor); x3 = KNCbea[t-1]/KGC[t-1] (the ratio of the BEA-valued to the GPIM-valued capital stock). The ratio x1 freezes at the last complete net-monetary-interest year — a known issue carried over unchanged from the predecessor build (CD2), preserved deliberately.</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>* x1 freezes at last complete NMINT_corp year; do NOT forward-fill (CD2 preserved behaviour).</t>
+          <t>* The ratio x1 freezes at the last complete corporate net-monetary-interest (NMINT) year; it is held, not forward-filled (behaviour preserved unchanged from the predecessor build, CD2).</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>`AS003`, `AS004`, `AS009`</t>
+          <t>`XS003`, `XS004`, `XS009`</t>
         </is>
       </c>
     </row>
@@ -8121,95 +8121,99 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>`V03_S603_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>`V03_S603` (the validate script) round-trip-checks the built series against the Appendix 6.8 source workbook at 1.0% tolerance. Per the readiness (adequacy) review (`CH6_ADEQUACY_REPORT.json`), the two ingestion blockers B2 (a National Income and Product Accounts table 7.11 FISIM re-mapping, handled by `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>- **Subseries (S603-A, -B, …)** — the individual ratio lines that make up series S603.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>- **x1 / x2 / x3** — the three decomposition ratios defined in the Construction section above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>- **GPIM** — the corrected capital-stock-and-surplus construction Shaikh uses across Chapter 6 (his integrated measure of the profit rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>- **NMINT** — net monetary interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>- **NIPA / BEA** — US National Income and Product Accounts / Bureau of Economic Analysis (KNCbea = the BEA-valued net capital stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>- **XS003 / XS004 / XS009** — appendix "extra series" recording GPIM construction internals; documentary lineage, not a live computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the load / process / validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset, retained for cross-checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4">
         <f>== EPR: S603_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t># S603 — Component Ratios x1, x2, x3 (Extension Provenance Record)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S603 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
-        </is>
-      </c>
-    </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
+          <t># S603 — Component Ratios x1, x2, x3 (Extension Provenance Record)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
+          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8223,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>## Worked Example</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8233,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>For S603, the Phase 5 round-trip validation reads `S603_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S603 values**. Instead, the extension re-fetches the underlying US national-accounts components (BEA National Income and Product Accounts / Fixed Asset accounts, IRS, Census) and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8243,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>&gt; **Scope note (Decision 0015).** The shipped data covers the book period only, transcribed verbatim from Shaikh's Appendix 6.8; the linked components XS003 / XS004 / XS009 are recorded as **documentary lineage**, not a live computation wired into this package. The component-refetch-and-recompute recipe below is the *designed forward extension* method; live GPIM re-computation is on the roadmap (Phase L) and has not yet been executed.</t>
         </is>
       </c>
     </row>
@@ -8249,129 +8253,273 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>3. Re-run the construction formula end-to-end.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4. Recompute XS003 (sectoral profit rates), XS004 (KNCcorp / KGCcorp), and XS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>## Failure Mode Table</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>## Worked Example</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>| Failure | Detection | Response |</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>|---------|-----------|----------|</t>
+          <t>For S603, the Phase 5 round-trip validation reads `S603_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>## No-Proxy Disclosure</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>## No-Synthetic Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>## Failure Mode Table</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>## Anti-Degradation Compliance</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Response |</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>|---------|-----------|----------|</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>## CD2 Divergence Pre-Disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>## Anti-Degradation Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Per the Anu Framework anti-degradation rule, the *designed* extension re-fetches the BEA / IRS / FRB component series and re-computes the formula end-to-end; splicing the published series is FORBIDDEN. (Book-period data ships as the verbatim Appendix 6.8 transcription; the recompute is the roadmap Phase L method — see the Scope note above.) The loader caches BEA / FRED responses with a 30-day time-to-live (book-period values are cached permanently).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>- **GPIM** — the corrected capital-stock-and-surplus construction Shaikh uses across Chapter 6 (his integrated measure of the profit rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>- **NMINT** — net monetary interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>- **NIPA / BEA / FA / IRS / FRB** — US National Income and Product Accounts / Bureau of Economic Analysis / its Fixed Asset accounts / Internal Revenue Service / Federal Reserve Board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>- **FISIM** — financial intermediation services indirectly measured (a national-accounts imputation affecting the T7.11 interest line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>- **XS003 / XS004 / XS009** — appendix "extra series" recording GPIM construction internals; documentary lineage, not a live computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset, retained for cross-checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase L** — Anu pipeline stages: Phase 5 = ingestion (the shipped book-period build); Phase L = the roadmap live-recompute extension stage.</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8925,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T23:02:54.547879+00:00</t>
+          <t>2026-07-02T06:24:53.080877+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S603_extenbook.xlsx
+++ b/extenbooks/S603_extenbook.xlsx
@@ -8925,7 +8925,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:24:53.080877+00:00</t>
+          <t>2026-07-11T03:44:25.717824+00:00</t>
         </is>
       </c>
     </row>
@@ -8940,11 +8940,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8967,6 +8967,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh Figure 6.3 (Ch6). Four dimensionless-ratio lines, 1947-2011: the monetary-interest factor (x1), the inventory factor (x2), the capital-stock revaluation factor (x3), and their product, which equals the ratio of the corrected to the conventional corporate profit rate (equation 6.11). Transcribed from Shaikh's Appendix 6.8 Table II-7. Construction-relevant analytical diagnostic that quantifies which correction drives the wedge in Figure 6.2; the x1 line freezes when corporate net monetary interest data run out (not forward-filled).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S603_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S603_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 6.3 source. x1 freezes when NMINT_corp from T7.11 incomplete (do NOT forward-fill). Source: Appendix Table 6.8.II.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dimensionless_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
